--- a/reports_excel/主管專用_【張希慈】部屬自評vs主管評對照表.xlsx
+++ b/reports_excel/主管專用_【張希慈】部屬自評vs主管評對照表.xlsx
@@ -969,7 +969,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>（覺得其實已經說很多了就這樣吧）</t>
+          <t>（部屬未填寫自評實例）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="82" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>其他創造的好事與預防的壞事</t>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>5月要繳交去年度工作報告及經費決算時，我有請會計協助填寫相關年度財報金額及資料，過去他會先寄檔案給我，我這邊確認完後才會請他用印，但此次會計填寫完後直接印出用印寄給我，原本要直接繳交出去，結果我心血來潮想說對一下數字，就發現了數字有誤，趕緊修正後再請會計用印，也因為我平常作業都會預留時間，所以不會因為臨時發現錯誤需要多幾天作業時間而導致時程延誤。</t>
+          <t>（部屬未填寫自評實例）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
